--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 33 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="P23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12010,8 +12010,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -20313,7 +20313,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1335,7 +1339,11 @@
       <c r="AB6" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -3072,7 +3080,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -5746,7 +5758,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5952,7 +5968,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7495,7 +7515,11 @@
       <c r="AB66" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -10383,7 +10407,11 @@
       <c r="AB94" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -14481,7 +14509,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14994,7 +15026,11 @@
       <c r="AB139" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC139" s="4" t="inlineStr"/>
+      <c r="AC139" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -16234,7 +16270,11 @@
       <c r="AB151" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC151" s="4" t="inlineStr"/>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -18088,7 +18128,11 @@
       <c r="AB169" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC169" s="4" t="inlineStr"/>
+      <c r="AC169" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 32 clubs short</t>
         </is>
       </c>
     </row>
@@ -14640,7 +14640,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q136" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -20555,7 +20555,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 32 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 31 clubs short</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="9" t="n">
         <v>0</v>
@@ -3663,8 +3663,8 @@
       <c r="S29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T29" s="9" t="n">
-        <v>0</v>
+      <c r="T29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U29" s="9" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5719,8 +5719,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P49" s="9" t="n">
-        <v>3</v>
+      <c r="P49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q49" s="10" t="n">
         <v>2</v>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9549,8 +9549,8 @@
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="9" t="n">
-        <v>0</v>
+      <c r="S86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T86" s="9" t="n">
         <v>0</v>
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q94" s="9" t="n">
         <v>0</v>
@@ -11867,7 +11867,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11937,8 +11937,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -14474,7 +14474,7 @@
         <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15714,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -15722,8 +15722,8 @@
       <c r="S146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T146" s="9" t="n">
-        <v>0</v>
+      <c r="T146" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U146" s="9" t="n">
         <v>0</v>
@@ -16821,7 +16821,7 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>10</v>
@@ -16876,8 +16876,8 @@
       <c r="T157" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U157" s="9" t="n">
-        <v>0</v>
+      <c r="U157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V157" s="9" t="n">
         <v>2</v>
@@ -17266,7 +17266,7 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q161" s="9" t="n">
         <v>0</v>
@@ -19491,7 +19491,7 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19534,8 +19534,8 @@
       <c r="P183" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q183" s="9" t="n">
-        <v>1</v>
+      <c r="Q183" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R183" s="9" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -19961,7 +19961,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -20192,7 +20192,7 @@
         <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20357,7 +20357,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -20621,7 +20621,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -20687,7 +20687,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -20885,7 +20885,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1312,8 +1312,8 @@
       <c r="S6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T6" s="9" t="n">
-        <v>0</v>
+      <c r="T6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="9" t="n">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1720,8 +1720,8 @@
       <c r="S10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T10" s="9" t="n">
-        <v>0</v>
+      <c r="T10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U10" s="9" t="n">
         <v>0</v>
@@ -2294,17 +2294,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2500,13 +2500,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -5156,7 +5156,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5205,8 +5205,8 @@
       <c r="R44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="9" t="n">
-        <v>1</v>
+      <c r="S44" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0</v>
@@ -5271,13 +5271,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
@@ -5897,13 +5897,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6028,14 +6028,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P52" s="9" t="n">
-        <v>3</v>
+      <c r="P52" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="10" t="n">
         <v>2</v>
@@ -6826,13 +6826,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7032,13 +7032,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7076,8 +7076,8 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -9199,13 +9199,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
@@ -9712,13 +9712,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T88" s="9" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>4</v>
@@ -10023,13 +10023,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10233,13 +10233,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
@@ -10334,13 +10334,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11293,8 +11293,8 @@
       <c r="S103" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12427,8 +12427,8 @@
       <c r="T114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
+      <c r="U114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V114" s="9" t="n">
         <v>0</v>
@@ -13536,16 +13536,16 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" s="9" t="n">
         <v>0</v>
@@ -13957,7 +13957,7 @@
         <v>0</v>
       </c>
       <c r="S129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" s="10" t="n">
         <v>1</v>
@@ -14852,13 +14852,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -15054,13 +15054,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -16397,13 +16397,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>0</v>
@@ -19600,13 +19600,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19739,8 +19739,8 @@
       <c r="S185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T185" s="9" t="n">
-        <v>0</v>
+      <c r="T185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U185" s="9" t="n">
         <v>0</v>
@@ -19961,7 +19961,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -19994,7 +19994,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20042,7 +20042,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -20225,7 +20225,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20258,13 +20258,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20588,7 +20588,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -20687,7 +20687,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -21182,7 +21182,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>

--- a/docs/d/67/inyear.xlsx
+++ b/docs/d/67/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>0</v>
@@ -2330,7 +2330,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" s="9" t="n">
         <v>0</v>
@@ -4602,8 +4602,8 @@
       <c r="W38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X38" s="9" t="n">
-        <v>2</v>
+      <c r="X38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5691,13 +5691,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5735,8 +5735,8 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>3</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -7549,17 +7549,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7594,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -9094,13 +9094,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>7</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13243,8 +13243,8 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
         <v>1</v>
@@ -13536,7 +13536,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>1</v>
@@ -15779,13 +15779,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" s="10" t="n">
         <v>1</v>
@@ -17057,7 +17057,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R159" s="9" t="n">
         <v>0</v>
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17742,13 +17742,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17786,8 +17786,8 @@
       <c r="U166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="9" t="n">
-        <v>3</v>
+      <c r="V166" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -18255,13 +18255,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>1</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
@@ -18566,13 +18566,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18809,8 +18809,8 @@
       <c r="T176" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U176" s="9" t="n">
-        <v>0</v>
+      <c r="U176" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V176" s="10" t="n">
         <v>4</v>
@@ -18873,13 +18873,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>0</v>
       </c>
       <c r="V177" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W177" s="9" t="n">
         <v>0</v>
@@ -19005,7 +19005,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q178" s="10" t="n">
         <v>2</v>
@@ -19600,13 +19600,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -20372,7 +20372,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -20753,7 +20753,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21050,7 +21050,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -21116,7 +21116,7 @@
         <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
